--- a/Framework_MWC_Testing/reports/results/ResultsData.xlsx
+++ b/Framework_MWC_Testing/reports/results/ResultsData.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Order" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Register" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Search" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Profile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Search" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Profile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Order" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,65 +771,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>PasswordConfirm</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -838,398 +813,642 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DH1</t>
+          <t>DK1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Nguyen_Pham_Nhat_Anh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>37</v>
+          <t>0359694333</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>905123456</v>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nguyen_Pham_Nhat_Anh</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>123 Lý Thường Kiệt</t>
+          <t>Nguyen_Pham_Nhat_Anh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quận 1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:11:49</t>
+          <t>25/10/2025 19:15:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DH2</t>
+          <t>DK2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>38</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>905123456</v>
+          <t>user_demo_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:12:43</t>
+          <t>25/10/2025 19:15:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DH3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
+          <t>DK3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>36</v>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quận 1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:13:39</t>
+          <t>25/10/2025 19:15:36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DH4</t>
+          <t>DK4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>user_demo_3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>36</v>
-      </c>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Phường An Khánh</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:14:34</t>
+          <t>25/10/2025 19:15:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DH5</t>
+          <t>DK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>user_demo_4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>905123456</v>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:15:28</t>
+          <t>25/10/2025 19:15:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DH6</t>
+          <t>DK6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>user_demo_5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>35</v>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nguyễn A</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3321156</v>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>456 DEF</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Quận 10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Phường 15</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SĐT không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>19/10/2025 11:16:23</t>
+          <t>25/10/2025 19:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DK7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>user_demo_6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DK8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>user_demo_7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>03!</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DK9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>user_demo_8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>03 45216789</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DK10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>user_demo_9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>03452167891</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DK11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>user_demo_10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DK12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>user_demo_11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1234567890abcdefghiklmno</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1234567890abcdefghiklmno</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DK13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>user_demo_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0912345679</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DK14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0352146789</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25/10/2025 19:17:01</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,40 +1474,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PasswordConfirm</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1297,642 +1501,355 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DK1</t>
+          <t>TK1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0359694333</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
+195.000 đ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:15:24</t>
+          <t>27/10/2025 07:40:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DK2</t>
+          <t>TK2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_demo_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>E196</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
+195.000 đ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:15:30</t>
+          <t>27/10/2025 07:40:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DK3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>TK3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giày</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Giày</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
+195.000 đ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:15:36</t>
+          <t>27/10/2025 07:40:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DK4</t>
+          <t>TK4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_demo_3</t>
+          <t>GIÀY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Giày</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
+195.000 đ</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:15:44</t>
+          <t>27/10/2025 07:40:47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DK5</t>
+          <t>TK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_demo_4</t>
+          <t>Giay the thao nam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Giày thể thao nam</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Giày Thể Thao Nam MWC 5827 - Giày Thể Thao Sneaker Nam Cổ Thấp Đi Phượt, Leo Núi, Chạy Bộ Siêu Bền Đẹp, Đa Phong Cách.
+380.000 đ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:15:52</t>
+          <t>27/10/2025 07:40:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DK6</t>
+          <t>TK6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_demo_5</t>
+          <t>Giay th</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:03</t>
+          <t>27/10/2025 07:41:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DK7</t>
+          <t>TK7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_demo_6</t>
+          <t>Bánh bao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:11</t>
+          <t>27/10/2025 07:41:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DK8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>user_demo_7</t>
-        </is>
-      </c>
+          <t>TK8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03!</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
+195.000 đ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:18</t>
+          <t>27/10/2025 07:41:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DK9</t>
+          <t>TK9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_demo_8</t>
+          <t>Giay!#$%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03 45216789</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:24</t>
+          <t>27/10/2025 07:42:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DK10</t>
+          <t>TK10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_demo_9</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03452167891</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:32</t>
+          <t>27/10/2025 07:42:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DK11</t>
+          <t>TK11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_demo_10</t>
+          <t>Màu đen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Màu đen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>Dép Nam MWC 9200 - Dép Nam Da Vân Hai Quai Chéo Hình Chữ X Màu Đen Tuyền Huyền Bí, Lịch Lãm, Sang Trọng.
+225.000 đ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DK12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>user_demo_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DK13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>user_demo_12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0912345679</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:16:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DK14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0352146789</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25/10/2025 19:17:01</t>
+          <t>27/10/2025 07:42:42</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,25 +1875,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FullName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1985,355 +1957,1114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TK1</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
-195.000 đ</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:10</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:56:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TK2</t>
+          <t>TT2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E196</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
-195.000 đ</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:19</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:57:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TK3</t>
+          <t>TT3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giày</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Giày</t>
-        </is>
-      </c>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156790</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:32</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:57:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TK4</t>
+          <t>TT4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GIÀY</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Giày</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
-        </is>
-      </c>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:47</t>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:57:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TK5</t>
+          <t>TT5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giay the thao nam</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Giày thể thao nam</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Giày Thể Thao Nam MWC 5827 - Giày Thể Thao Sneaker Nam Cổ Thấp Đi Phượt, Leo Núi, Chạy Bộ Siêu Bền Đẹp, Đa Phong Cách.
-380.000 đ</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:57</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:58:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TK6</t>
+          <t>TT6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giay th</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:14</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:58:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TK7</t>
+          <t>TT7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bánh bao</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anh1@</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:31</t>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:59:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TK8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>TT8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
+          <t>anh1@@</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>03321156790</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:47</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>27/10/2025 07:59:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TK9</t>
+          <t>TT9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Giay!#$%</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anh1@gmail.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:06</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:00:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TK10</t>
+          <t>TT10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:21</t>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:01:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TK11</t>
+          <t>TT11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Màu đen</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Màu đen</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dép Nam MWC 9200 - Dép Nam Da Vân Hai Quai Chéo Hình Chữ X Màu Đen Tuyền Huyền Bí, Lịch Lãm, Sang Trọng.
-225.000 đ</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>abcd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:42</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:01:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TT12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TT13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0332115678987</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:02:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TT14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>!#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>27/10/2025 08:03:19</t>
         </is>
       </c>
     </row>
@@ -2348,7 +3079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,80 +3090,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>District</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -2441,1198 +3157,420 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>DH1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>bạc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>905123456.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>123 Lý Thường Kiệt</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Huyện Châu Thành</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Xã Đông Phước A</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:56:48</t>
+          <t>06/12/2025 23:01:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>DH2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>đen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>905123456.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>123 ABC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>TP. Hồ Chí Minh</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Không có thông báo hiển thị.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:08</t>
+          <t>06/12/2025 23:03:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TT3</t>
+          <t>DH3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03321156790</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>123 ABC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TP. Hồ Chí Minh</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Quận 2</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:25</t>
+          <t>06/12/2025 23:04:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>DH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>905123456.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>Quận 2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Phường An Khánh</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Huyện Châu Thành</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Xã Đông Phước A</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:55</t>
+          <t>06/12/2025 23:04:33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TT5</t>
+          <t>DH5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>bạc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>905123456.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>123 ABC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Chọn Tỉnh/Thành</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>Chọn Quận/huyện</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Chọn Xã/Phường</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Huyện Châu Thành</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:58:18</t>
+          <t>06/12/2025 23:05:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT6</t>
+          <t>DH6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>bạc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Nguyễn A</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>3321156.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>456 DEF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>Quận 10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>Phường 15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>SĐT không đúng định dạng</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:58:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TT7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>anh1@</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:59:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TT8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>anh1@@</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>03321156790</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:59:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TT9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>anh1@gmail.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:00:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:01:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TT11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>abcd</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:01:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TT12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:02:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TT13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0332115678987</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:02:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TT14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>!#$%^&amp;*()</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:03:19</t>
+          <t>06/12/2025 23:05:38</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/reports/results/ResultsData.xlsx
+++ b/Framework_MWC_Testing/reports/results/ResultsData.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Order" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Search" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Profile" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Order" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Login" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Profile" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,30 +440,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FullName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -472,280 +507,398 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DN1</t>
+          <t>DH1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>905123456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25/10/2025 13:11:57</t>
+          <t>123 Lý Thường Kiệt</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:11:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DN2</t>
+          <t>DH2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ÁNH DƯƠNG PHẠM</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>905123456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25/10/2025 13:12:16</t>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:12:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DN3</t>
+          <t>DH3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>anhduong123</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>anhduongpham</t>
-        </is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25/10/2025 13:12:36</t>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:12:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DN4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>DH4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anhduong@124</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>25/10/2025 13:12:42</t>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>905123456</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Phường An Khánh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:13:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DN5</t>
+          <t>DH5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>905123456</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25/10/2025 13:13:04</t>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:13:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DN6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
+          <t>DH6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+          <t>Nguyễn A</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3321156</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25/10/2025 13:13:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DN7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>anh</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>anhduong@125</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>25/10/2025 13:13:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DN8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>anhduong</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>25/10/2025 13:13:24</t>
+          <t>456 DEF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Quận 10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Phường Cầu Ông Lãnh</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SĐT không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16/12/2025 23:14:19</t>
         </is>
       </c>
     </row>
@@ -818,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
+          <t>Phạm Dương Ánh Ngọc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0359694333</t>
+          <t>0359694533</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -838,12 +991,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
+          <t>Phạm Dương Ánh Ngọc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nguyen_Pham_Nhat_Anh</t>
+          <t>Phạm Dương Ánh Ngọc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -853,7 +1006,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25/10/2025 19:15:24</t>
+          <t>19/12/2025 14:53:51</t>
         </is>
       </c>
     </row>
@@ -896,7 +1049,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25/10/2025 19:15:30</t>
+          <t>19/12/2025 14:53:58</t>
         </is>
       </c>
     </row>
@@ -939,7 +1092,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25/10/2025 19:15:36</t>
+          <t>19/12/2025 14:54:09</t>
         </is>
       </c>
     </row>
@@ -982,7 +1135,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25/10/2025 19:15:44</t>
+          <t>19/12/2025 14:54:16</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1178,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25/10/2025 19:15:52</t>
+          <t>19/12/2025 14:54:25</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1225,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:03</t>
+          <t>19/12/2025 14:54:33</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1272,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:11</t>
+          <t>19/12/2025 14:54:44</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1319,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:18</t>
+          <t>19/12/2025 14:54:53</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1366,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:24</t>
+          <t>19/12/2025 14:54:59</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1413,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:32</t>
+          <t>19/12/2025 14:55:06</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1460,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:39</t>
+          <t>19/12/2025 14:55:19</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1477,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0912345679</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1354,7 +1507,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:47</t>
+          <t>19/12/2025 14:55:25</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1554,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25/10/2025 19:16:54</t>
+          <t>19/12/2025 14:55:31</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1571,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0352146789</t>
+          <t>035214679</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1448,7 +1601,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25/10/2025 19:17:01</t>
+          <t>19/12/2025 14:55:37</t>
         </is>
       </c>
     </row>
@@ -1506,17 +1659,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
 195.000 đ</t>
         </is>
       </c>
@@ -1527,7 +1680,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:10</t>
+          <t>19/12/2025 15:21:14</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1697,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
 195.000 đ</t>
         </is>
       </c>
@@ -1560,7 +1713,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:19</t>
+          <t>19/12/2025 15:21:20</t>
         </is>
       </c>
     </row>
@@ -1582,8 +1735,8 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
+          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
+275.000 đ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1593,7 +1746,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:32</t>
+          <t>19/12/2025 15:21:30</t>
         </is>
       </c>
     </row>
@@ -1615,8 +1768,8 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
+          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
+275.000 đ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1626,7 +1779,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:47</t>
+          <t>19/12/2025 15:21:37</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1812,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27/10/2025 07:40:57</t>
+          <t>19/12/2025 15:21:44</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1844,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:14</t>
+          <t>19/12/2025 15:21:51</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1876,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:31</t>
+          <t>19/12/2025 15:22:01</t>
         </is>
       </c>
     </row>
@@ -1741,8 +1894,8 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G295 - Sandal Gót Trụ Tròn 5cm, Quai Mảnh Phối Nơ Nhỏ Xinh Thanh Lịch, Nữ Tính, Thời Trang.
-195.000 đ</t>
+          <t>Dép Nữ MWC 8640 - Dép Da Thời Trang Nữ Cao Cấp, Quai Ngang Cách Điệu Phối Khoá Kim Loại Sang Trọng, Nữ Tính, Thời Trang.
+150.000 đ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1752,7 +1905,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27/10/2025 07:41:47</t>
+          <t>19/12/2025 15:22:09</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1937,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:06</t>
+          <t>19/12/2025 15:22:22</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1954,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Đế Đúc Nguyên Khối, Quai Ngang To Bản Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái.</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1816,7 +1969,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:21</t>
+          <t>19/12/2025 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1838,8 +1991,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dép Nam MWC 9200 - Dép Nam Da Vân Hai Quai Chéo Hình Chữ X Màu Đen Tuyền Huyền Bí, Lịch Lãm, Sang Trọng.
-225.000 đ</t>
+          <t>BALO MWC 1267 - Balo Unisex Phối Màu Đen, Be Thanh Lịch, Vừa Thời Trang Vừa Tiện Dụng Đựng Mọi Thứ Bạn Cần.
+180.000 đ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1849,7 +2002,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27/10/2025 07:42:42</t>
+          <t>19/12/2025 15:22:37</t>
         </is>
       </c>
     </row>
@@ -1864,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,75 +2033,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1957,7 +2060,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>DN1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1967,548 +2070,240 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:56:48</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:23:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>DN2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>ÁNH DƯƠNG PHẠM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Ánh Dương Phạm</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Quận 1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:08</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:24:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TT3</t>
+          <t>DN3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>anhduongpham</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>anhduong123</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03321156790</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:25</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:25:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TT4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
+          <t>DN4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>anhduong@124</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:57:55</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:25:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TT5</t>
+          <t>DN5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
+          <t>anhduongpham</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:58:18</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:25:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
+          <t>DN6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Chọn Tỉnh/Thành</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Chọn Quận/huyện</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:58:47</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:26:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TT7</t>
+          <t>DN7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>anh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>anhduong@125</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anh1@</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:59:15</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:26:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TT8</t>
+          <t>DN8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2518,553 +2313,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>anhduong</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anh1@@</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>03321156790</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>27/10/2025 07:59:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TT9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>anh1@gmail.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:00:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:01:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TT11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>abcd</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2005</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:01:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TT12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:02:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TT13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0332115678987</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2007</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:02:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TT14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>!#$%^&amp;*()</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>27/10/2025 08:03:19</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20/12/2025 00:26:25</t>
         </is>
       </c>
     </row>
@@ -3079,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3090,65 +2359,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -3157,420 +2436,1146 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DH1</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bạc</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>905123456.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>123 Lý Thường Kiệt</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>Phường Lái Hiếu</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>lâm đồng</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>06/12/2025 23:01:56</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:14:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DH2</t>
+          <t>TT2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>đen</t>
+          <t>anhduong1@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>03321156788</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>905123456.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Quận 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Phường Bến Nghé</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Không có thông báo hiển thị.</t>
+          <t>đà nẵng</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>06/12/2025 23:03:26</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:14:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DH3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
+          <t>TT3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bạc</t>
+          <t>duongduong@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>03321156790</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>TP Cần Thơ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Quận Ninh Kiều</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường An Bình</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>huế</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>06/12/2025 23:04:08</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:14:45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DH4</t>
+          <t>TT4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bạc</t>
-        </is>
-      </c>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>905123456.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Quận 2</t>
+          <t>Đồng Nai</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Phường An Khánh</t>
+          <t>Quận Ô Môn</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường Long Hưng</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>gia lai</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>06/12/2025 23:04:33</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:15:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DH5</t>
+          <t>TT5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Dương</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bạc</t>
+          <t>anhanh@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>03321156770</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>905123456.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>123 ABC</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
+          <t>Phường Lái Hiếu</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>06/12/2025 23:05:02</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:15:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DH6</t>
+          <t>TT6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm Thị</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bạc</t>
+          <t>anh12@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nguyễn A</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3321156.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>456 DEF</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TT7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>anh1@</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>03321156754</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Thành phố Tây Ninh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phường 1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hà nội</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:17:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TT8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anh1@@</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>03321156790</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Huyện Trà Ôn</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Thị trấn Trà Ôn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vĩnh tuy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TT9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>anh1@gmail.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>sóc sơn</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:18:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bình Phước</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Huyện Lộc Ninh</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Xã Lộc An</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>móng cái</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:19:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TT11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Phạm Dương</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>lạng sơn</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TT12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>phamanh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tiền Giang</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Thành phố Mỹ Tho</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phường 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quỳnh phụ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:19:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TT13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Phạm Ánh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>phamanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0332115678987</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>thái bình</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TT14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>!#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Quận 10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Phường 15</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SĐT không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nghĩa lộ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>06/12/2025 23:05:38</t>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>20/12/2025 01:22:53</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/reports/results/ResultsData.xlsx
+++ b/Framework_MWC_Testing/reports/results/ResultsData.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Product_Review" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Search" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Login" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Profile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Profile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Order" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Register" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,65 +441,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -507,398 +493,696 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DH1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>35</v>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>123 Lý Thường Kiệt</t>
-        </is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Gửi bình luận thành công!</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Gửi bình luận thành công!</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:11:31</t>
+          <t>21/12/2025 01:30:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DH2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>36</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:12:09</t>
+          <t>21/12/2025 01:30:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DH3</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>39</v>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:12:47</t>
+          <t>21/12/2025 01:31:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DH4</t>
+          <t>DG4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>36</v>
-      </c>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Quận 2</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Phường An Khánh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:13:15</t>
+          <t>21/12/2025 01:31:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DH5</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>39</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:13:51</t>
+          <t>21/12/2025 01:32:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DH6</t>
+          <t>DG6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>37</v>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nguyễn A</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3321156</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>456 DEF</t>
-        </is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Quận 10</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Phường Cầu Ông Lãnh</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SĐT không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+          <t>21/12/2025 01:32:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DG7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>16/12/2025 23:14:19</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DG8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abdc</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:34:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DG9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>!@#$%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:34:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DG10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>032145678999</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:35:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DG11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>anh1@_x000d_</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi khi chạy testcase: Không thể mở sản phẩm đầu tiên [open_first_product]: Message: 
+</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:35:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DG12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>anh1@@_x000d_</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:36:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DG13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>anh1@gmail._x000d_</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>21/12/2025 01:36:43</t>
         </is>
       </c>
     </row>
@@ -913,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,35 +1213,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PasswordConfirm</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -966,642 +1240,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DK1</t>
+          <t>DN1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Dương Ánh Ngọc</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0359694533</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Phạm Dương Ánh Ngọc</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phạm Dương Ánh Ngọc</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:53:51</t>
+          <t>21/12/2025 23:03:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DK2</t>
+          <t>DN2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_demo_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>ÁNH DƯƠNG PHẠM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:53:58</t>
+          <t>21/12/2025 23:03:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DK3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>DN3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>anhduongpham</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>anhduong123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:09</t>
+          <t>21/12/2025 23:04:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DK4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>user_demo_3</t>
-        </is>
-      </c>
+          <t>DN4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>anhduong@124</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:16</t>
+          <t>21/12/2025 23:04:51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DK5</t>
+          <t>DN5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_demo_4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
+          <t>anhduongpham</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:25</t>
+          <t>21/12/2025 23:05:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DK6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>user_demo_5</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>091</t>
-        </is>
-      </c>
+          <t>DN6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:33</t>
+          <t>21/12/2025 23:05:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DK7</t>
+          <t>DN7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_demo_6</t>
+          <t>anh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>anhduong@125</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:44</t>
+          <t>21/12/2025 23:05:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DK8</t>
+          <t>DN8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_demo_7</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03!</t>
+          <t>anhduong</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DK9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>user_demo_8</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>03 45216789</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:54:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DK10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>user_demo_9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>03452167891</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:55:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DK11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>user_demo_10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:55:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DK12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>user_demo_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0912345679</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:55:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DK13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>user_demo_12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0912345679</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:55:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DK14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>035214679</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>19/12/2025 14:55:37</t>
+          <t>21/12/2025 23:05:40</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:14</t>
+          <t>21/12/2025 23:18:22</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1625,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:20</t>
+          <t>21/12/2025 23:18:34</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1658,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:30</t>
+          <t>21/12/2025 23:18:42</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:37</t>
+          <t>21/12/2025 23:18:55</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1724,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:44</t>
+          <t>21/12/2025 23:19:07</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1756,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19/12/2025 15:21:51</t>
+          <t>21/12/2025 23:19:15</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19/12/2025 15:22:01</t>
+          <t>21/12/2025 23:19:25</t>
         </is>
       </c>
     </row>
@@ -1894,8 +1806,8 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dép Nữ MWC 8640 - Dép Da Thời Trang Nữ Cao Cấp, Quai Ngang Cách Điệu Phối Khoá Kim Loại Sang Trọng, Nữ Tính, Thời Trang.
-150.000 đ</t>
+          <t>Dép Nữ MWC 8620 - Dép Đế Bệt Nữ Mũi Tròn, Quai Da PU Bóng Mảnh Cách Điệu Đi Dạo Phố, Đi Làm Đơn Giản, Thanh Lịch.
+125.000 đ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1905,7 +1817,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19/12/2025 15:22:09</t>
+          <t>21/12/2025 23:19:39</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1849,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19/12/2025 15:22:22</t>
+          <t>21/12/2025 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1881,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19/12/2025 15:22:30</t>
+          <t>21/12/2025 23:19:57</t>
         </is>
       </c>
     </row>
@@ -2002,7 +1914,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19/12/2025 15:22:37</t>
+          <t>21/12/2025 23:20:07</t>
         </is>
       </c>
     </row>
@@ -2017,7 +1929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,30 +1940,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -2060,280 +2017,1064 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DN1</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>anh1@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:23:55</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Thị xã Ngã Bảy</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Phường Lái Hiếu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>lâm đồng</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:26:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DN2</t>
+          <t>TT2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ÁNH DƯƠNG PHẠM</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>anhduong1@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>03321156788</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:24:42</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>đà nẵng</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:26:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DN3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
+          <t>TT3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>anhduong123</t>
+          <t>duongduong@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
+          <t>03321156790</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:25:28</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TP Cần Thơ</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Quận Ninh Kiều</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Phường An Bình</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>huế</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:26:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DN4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>anhduong@124</t>
-        </is>
-      </c>
+          <t>TT4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:25:37</t>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Đồng Nai</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Quận Ô Môn</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Phường Long Hưng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>gia lai</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:27:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DN5</t>
+          <t>TT5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Phạm Dương</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>anhanh@gmail.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>03321156770</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:25:58</t>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Thị xã Ngã Bảy</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Phường Lái Hiếu</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:27:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DN6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>TT6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm Thị</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>anh12@gmail.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>03321156789</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:26:03</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:28:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DN7</t>
+          <t>TT7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>anh</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anhduong@125</t>
+          <t>anh1@</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+          <t>03321156754</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:26:18</t>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Thành phố Tây Ninh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phường 1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hà nội</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:29:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DN8</t>
+          <t>TT8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>anhduong</t>
+          <t>anh1@@</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+          <t>03321156790</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>20/12/2025 00:26:25</t>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1997</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Huyện Trà Ôn</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Thị trấn Trà Ôn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vĩnh tuy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:30:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TT9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>anh1@gmail.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>sóc sơn</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:31:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bình Phước</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Huyện Lộc Ninh</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Xã Lộc An</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>móng cái</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TT11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Phạm Dương</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>lạng sơn</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:32:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TT12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>phamanh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tiền Giang</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Thành phố Mỹ Tho</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phường 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quỳnh phụ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TT13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Phạm Ánh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>phamanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0332115678987</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>thái bình</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:32:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TT14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>!#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nghĩa lộ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:33:23</t>
         </is>
       </c>
     </row>
@@ -2348,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,75 +3100,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>District</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -2436,1146 +3167,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>DH1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>905123456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>123 Lý Thường Kiệt</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Thị xã Ngã Bảy</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phường Lái Hiếu</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>lâm đồng</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:14:00</t>
+          <t>21/12/2025 23:35:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>DH2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anhduong1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>03321156788</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>905123456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>123 ABC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>đà nẵng</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:14:25</t>
+          <t>21/12/2025 23:36:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TT3</t>
+          <t>DH3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Quận 1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:37:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DH4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>905123456</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Phường An Khánh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:37:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DH5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>905123456</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:38:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DH6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nguyễn A</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3321156</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>456 DEF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Quận 10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Phường Cầu Ông Lãnh</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SĐT không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:38:38</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Testcase</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PasswordConfirm</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DK1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Ngọc Lan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0359694333</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Ngọc Lan</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DK2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>user_demo_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DK3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>duongduong@gmail.com</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>03321156790</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TP Cần Thơ</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Quận Ninh Kiều</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Phường An Bình</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>huế</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:14:45</t>
+          <t>21/12/2025 23:41:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>DK4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
+          <t>user_demo_3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Đồng Nai</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Quận Ô Môn</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Phường Long Hưng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>gia lai</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:15:20</t>
+          <t>21/12/2025 23:41:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TT5</t>
+          <t>DK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phạm Dương</t>
+          <t>user_demo_4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anhanh@gmail.com</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03321156770</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Thị xã Ngã Bảy</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Phường Lái Hiếu</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:15:38</t>
+          <t>21/12/2025 23:42:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT6</t>
+          <t>DK6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm Thị</t>
+          <t>user_demo_5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anh12@gmail.com</t>
+          <t>091</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Chọn Quận/huyện</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:16:26</t>
+          <t>21/12/2025 23:42:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TT7</t>
+          <t>DK7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anh1@</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>03321156754</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tây Ninh</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Thành phố Tây Ninh</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Phường 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hà nội</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:17:10</t>
+          <t>21/12/2025 23:42:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TT8</t>
+          <t>DK8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>user_demo_7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>anh1@@</t>
+          <t>03!</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>03321156790</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Vĩnh Long</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Huyện Trà Ôn</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Thị trấn Trà Ôn</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>vĩnh tuy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:17:47</t>
+          <t>21/12/2025 23:42:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TT9</t>
+          <t>DK9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>user_demo_8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>anh1@gmail.</t>
+          <t>03 45216789</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03321156789</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>sóc sơn</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:18:27</t>
+          <t>21/12/2025 23:42:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TT10</t>
+          <t>DK10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ánh Dương</t>
+          <t>user_demo_9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>03452167891</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bình Phước</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Huyện Lộc Ninh</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Xã Lộc An</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>móng cái</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:19:08</t>
+          <t>21/12/2025 23:42:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TT11</t>
+          <t>DK11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Phạm Dương</t>
+          <t>user_demo_10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>abcd</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>lạng sơn</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:19:27</t>
+          <t>21/12/2025 23:43:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TT12</t>
+          <t>DK12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>user_demo_11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phamanh1@gmail.com</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>1234567890abcdefghiklmno</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>1234567890abcdefghiklmno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tiền Giang</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Thành phố Mỹ Tho</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Phường 10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>quỳnh phụ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:19:43</t>
+          <t>21/12/2025 23:43:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TT13</t>
+          <t>DK13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Phạm Ánh</t>
+          <t>user_demo_12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>phamanh@gmail.com</t>
+          <t>0912345679</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0332115678987</t>
+          <t>12345678</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>mật khẩu không giống nhau</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>mật khẩu không giống nhau</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>thái bình</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:20:03</t>
+          <t>21/12/2025 23:43:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TT14</t>
+          <t>DK14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
+          <t>0352146789</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>!#$%^&amp;*()</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>nghĩa lộ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>20/12/2025 01:22:53</t>
+          <t>21/12/2025 23:43:39</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/reports/results/ResultsData.xlsx
+++ b/Framework_MWC_Testing/reports/results/ResultsData.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Product_Review" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Login" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Search" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Profile" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Order" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Register" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Order" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Profile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Product_Review" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,50 +441,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -493,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>DN1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,362 +483,240 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:30:27</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:48:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DG2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>DN2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ÁNH DƯƠNG PHẠM</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:30:56</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:49:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>DN3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>anhduongpham</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>anhduong123</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>anhduongpham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:31:24</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:50:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
+          <t>DN4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0321456789</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>anhduong@124</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:31:53</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:50:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DG5</t>
+          <t>DN5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
+          <t>anhduongpham</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:32:23</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:50:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DG6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
+          <t>DN6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:32:50</t>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:50:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DG7</t>
+          <t>DN7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>anh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>anhduong@125</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:33:28</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:51:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DG8</t>
+          <t>DN8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -868,321 +726,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abdc</t>
+          <t>anhduong</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:34:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DG9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>!@#$%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>anhduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:34:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DG10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>032145678999</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>anhduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:35:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DG11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>anh1@_x000d_</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Email không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lỗi khi chạy testcase: Không thể mở sản phẩm đầu tiên [open_first_product]: Message: 
-</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:35:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DG12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>anh1@@_x000d_</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Email không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:36:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DG13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>anh1@gmail._x000d_</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Email không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>21/12/2025 01:36:43</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:51:09</t>
         </is>
       </c>
     </row>
@@ -1197,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,25 +777,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PasswordConfirm</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1240,280 +814,664 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DN1</t>
+          <t>DK1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Phạm Ánh Ngọc Lan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>0359694333</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Phạm Ánh Ngọc Lan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:03:04</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:51:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DN2</t>
+          <t>DK2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ÁNH DƯƠNG PHẠM</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
+          <t>user_demo_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:03:53</t>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:51:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DN3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
+          <t>DK3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>anhduong123</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:04:41</t>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:51:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DN4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>DK4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>user_demo_3</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anhduong@124</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:04:51</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:52:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DN5</t>
+          <t>DK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>anhduongpham</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>user_demo_4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi khi chạy testcase: Message: 
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff75d0f88e5
+	0x7ff75d0f8940
+	0x7ff75ced165d
+	0x7ff75cf29a33
+	0x7ff75cf29d3c
+	0x7ff75cf7df67
+	0x7ff75cf7ac97
+	0x7ff75cf1ac29
+	0x7ff75cf1ba93
+	0x7ff75d410640
+	0x7ff75d40af80
+	0x7ff75d4296e6
+	0x7ff75d115de4
+	0x7ff75d11ed8c
+	0x7ff75d102004
+	0x7ff75d1021b5
+	0x7ff75d0e7ee2
+	0x7ffe731ae8d7
+	0x7ffe7486c53c
+</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:05:12</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:53:20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DN6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>DK6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>user_demo_5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/12/2025 23:05:20</t>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:53:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DN7</t>
+          <t>DK7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>anh</t>
+          <t>user_demo_6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anhduong@125</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21/12/2025 23:05:32</t>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:53:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DN8</t>
+          <t>DK8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>user_demo_7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>03!</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:53:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DK9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>user_demo_8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>03 45216789</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:53:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DK10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>user_demo_9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>03452167891</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:54:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DK11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>user_demo_10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:55:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DK12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>user_demo_11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1234567890abcdefghiklmno</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1234567890abcdefghiklmno</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:55:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DK13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>user_demo_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0912345679</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:55:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DK14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Ánh Dương Phạm</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>anhduong</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:05:40</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0352146789</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>21/12/2025 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1550,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:18:22</t>
+          <t>21/12/2025 23:57:20</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1583,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:18:34</t>
+          <t>21/12/2025 23:57:30</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1616,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:18:42</t>
+          <t>21/12/2025 23:57:43</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1649,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:18:55</t>
+          <t>21/12/2025 23:57:56</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1682,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:07</t>
+          <t>21/12/2025 23:58:06</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1714,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:15</t>
+          <t>21/12/2025 23:58:14</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1746,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:25</t>
+          <t>21/12/2025 23:58:25</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1775,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:39</t>
+          <t>21/12/2025 23:58:36</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1807,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:48</t>
+          <t>21/12/2025 23:58:46</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1839,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21/12/2025 23:19:57</t>
+          <t>21/12/2025 23:58:54</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/12/2025 23:20:07</t>
+          <t>21/12/2025 23:59:05</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1940,75 +1898,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>District</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -2017,1064 +1965,398 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>DH1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2000</v>
+        <v>905123456</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>123 Lý Thường Kiệt</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Thị xã Ngã Bảy</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phường Lái Hiếu</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>lâm đồng</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:26:26</t>
+          <t>22/12/2025 00:01:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>DH2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anhduong1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>03321156788</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2000</v>
+        <v>905123456</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>đà nẵng</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:26:41</t>
+          <t>22/12/2025 00:01:57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TT3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>DH3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>duongduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>03321156790</t>
-        </is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2001</v>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TP Cần Thơ</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Quận Ninh Kiều</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phường An Bình</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>huế</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:26:58</t>
+          <t>22/12/2025 00:02:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>DH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2003</v>
+        <v>905123456</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Đồng Nai</t>
+          <t>Quận 2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Quận Ô Môn</t>
+          <t>Phường An Khánh</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phường Long Hưng</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>gia lai</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:27:30</t>
+          <t>22/12/2025 00:03:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TT5</t>
+          <t>DH5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phạm Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anhanh@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>03321156770</t>
-        </is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2005</v>
+        <v>905123456</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Chọn Quận/huyện</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Thị xã Ngã Bảy</t>
+          <t>Chọn Xã/Phường</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phường Lái Hiếu</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:27:46</t>
+          <t>22/12/2025 00:03:45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT6</t>
+          <t>DH6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm Thị</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anh12@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nguyễn A</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1999</v>
+        <v>3321156</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>456 DEF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>Quận 10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Phường Cầu Ông Lãnh</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>SĐT không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Đặt hàng thành công!</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:28:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TT7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>anh1@</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>03321156754</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1995</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tây Ninh</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Thành phố Tây Ninh</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Phường 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hà nội</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:29:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TT8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>anh1@@</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>03321156790</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1997</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Vĩnh Long</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Huyện Trà Ôn</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Thị trấn Trà Ôn</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>vĩnh tuy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:30:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TT9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>anh1@gmail.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2003</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>sóc sơn</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:31:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2004</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bình Phước</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Huyện Lộc Ninh</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Xã Lộc An</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>móng cái</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:31:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TT11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Phạm Dương</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>anhduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>abcd</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2005</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>lạng sơn</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:32:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TT12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>phamanh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Tiền Giang</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Thành phố Mỹ Tho</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Phường 10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>quỳnh phụ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:32:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TT13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Phạm Ánh</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>phamanh@gmail.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0332115678987</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2007</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>thái bình</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:32:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TT14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>!#$%^&amp;*()</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>nghĩa lộ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:33:23</t>
+          <t>22/12/2025 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3089,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,65 +2382,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -3167,398 +2459,1064 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DH1</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>35</v>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>123 Lý Thường Kiệt</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>Phường Lái Hiếu</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>lâm đồng</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:35:49</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:04:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DH2</t>
+          <t>TT2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>36</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>anhduong1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03321156788</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Quận 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Phường Bến Nghé</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>đà nẵng</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:36:24</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:05:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DH3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
+          <t>TT3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>39</v>
+          <t>duongduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>03321156790</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>TP Cần Thơ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Quận Ninh Kiều</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường An Bình</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>huế</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:37:03</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:05:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DH4</t>
+          <t>TT4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>36</v>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2003</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Quận 2</t>
+          <t>Đồng Nai</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Phường An Khánh</t>
+          <t>Quận Ô Môn</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường Long Hưng</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>gia lai</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:37:32</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:06:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DH5</t>
+          <t>TT5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Dương</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>39</v>
+          <t>anhanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>03321156770</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Chọn Tỉnh/Thành</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2005</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
+          <t>Phường Lái Hiếu</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>21/12/2025 23:38:12</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:06:24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DH6</t>
+          <t>TT6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm Thị</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>37</v>
+          <t>anh12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nguyễn A</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3321156</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>456 DEF</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:07:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TT7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>anh1@</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>03321156754</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Thành phố Tây Ninh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phường 1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hà nội</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:07:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TT8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anh1@@</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>03321156790</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1997</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Huyện Trà Ôn</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Thị trấn Trà Ôn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vĩnh tuy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:08:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TT9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>anh1@gmail.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>sóc sơn</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:09:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bình Phước</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Huyện Lộc Ninh</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Xã Lộc An</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>móng cái</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TT11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Phạm Dương</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>lạng sơn</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TT12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>phamanh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tiền Giang</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Thành phố Mỹ Tho</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phường 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quỳnh phụ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:10:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TT13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Phạm Ánh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>phamanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0332115678987</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>thái bình</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:10:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TT14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>!#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Quận 10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Phường Cầu Ông Lãnh</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SĐT không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nghĩa lộ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:38:38</t>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:10:59</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3584,7 +3542,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3594,30 +3552,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PasswordConfirm</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -3626,642 +3594,721 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DK1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Ngọc Lan</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0359694333</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Ngọc Lan</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Gửi bình luận thành công!</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:41:32</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:16:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DK2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>user_demo_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:41:40</t>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:17:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DK3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:41:48</t>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:17:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DK4</t>
+          <t>DG4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_demo_3</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+          <t>2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:41:57</t>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:17:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DK5</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_demo_4</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:06</t>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:18:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DK6</t>
+          <t>DG6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_demo_5</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Vui lòng nhập!</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:15</t>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:18:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DK7</t>
+          <t>DG7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_demo_6</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:26</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:19:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DK8</t>
+          <t>DG8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_demo_7</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03!</t>
+          <t>abdc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:34</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:19:45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DK9</t>
+          <t>DG9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_demo_8</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03 45216789</t>
+          <t>!@#$%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:43</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:20:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DK10</t>
+          <t>DG10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_demo_9</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03452167891</t>
+          <t>032145678999</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>số điện thoại không đúng định dạng!</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Số điện thoại không hợp lệ</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21/12/2025 23:42:54</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:20:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DK11</t>
+          <t>DG11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_demo_10</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>anh1@_x000d_</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Email không đúng định dạng</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21/12/2025 23:43:03</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:21:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DK12</t>
+          <t>DG12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_demo_11</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1234567890abcdefghiklmno</t>
+          <t>anh1@@_x000d_</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1234567890abcdefghiklmno</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Email không đúng định dạng</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21/12/2025 23:43:15</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:21:58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DK13</t>
+          <t>DG13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_demo_12</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0912345679</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12345678</t>
+          <t>anh1@gmail._x000d_</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>mật khẩu không giống nhau</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>mật khẩu không giống nhau</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Email không đúng định dạng</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21/12/2025 23:43:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DK14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0352146789</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:43:39</t>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>22/12/2025 00:22:25</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/reports/results/ResultsData.xlsx
+++ b/Framework_MWC_Testing/reports/results/ResultsData.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Search" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Order" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Profile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Product_Review" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Search" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Product_Review" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Profile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Order" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Register" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:48:26</t>
+          <t>23/12/2025 09:43:36</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:49:18</t>
+          <t>23/12/2025 09:44:40</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:50:09</t>
+          <t>23/12/2025 09:45:36</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:50:20</t>
+          <t>23/12/2025 09:45:45</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21/12/2025 23:50:42</t>
+          <t>23/12/2025 09:46:08</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/12/2025 23:50:50</t>
+          <t>23/12/2025 09:46:19</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21/12/2025 23:51:01</t>
+          <t>23/12/2025 09:46:35</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21/12/2025 23:51:09</t>
+          <t>23/12/2025 09:46:51</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,40 +772,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PasswordConfirm</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -814,664 +799,355 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DK1</t>
+          <t>TK1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Ngọc Lan</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0359694333</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
+195.000 đ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Ngọc Lan</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:51:42</t>
+          <t>23/12/2025 10:03:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DK2</t>
+          <t>TK2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_demo_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>E196</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
+195.000 đ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:51:50</t>
+          <t>23/12/2025 10:04:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DK3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>TK3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giày</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Giày</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
+275.000 đ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:51:58</t>
+          <t>23/12/2025 10:04:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DK4</t>
+          <t>TK4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_demo_3</t>
+          <t>GIÀY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Giày</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
+275.000 đ</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:52:07</t>
+          <t>23/12/2025 10:04:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DK5</t>
+          <t>TK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_demo_4</t>
+          <t>Giay the thao nam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Giày thể thao nam</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Giày Thể Thao Nam MWC 5827 - Giày Thể Thao Sneaker Nam Cổ Thấp Đi Phượt, Leo Núi, Chạy Bộ Siêu Bền Đẹp, Đa Phong Cách.
+380.000 đ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lỗi khi chạy testcase: Message: 
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff75d0f88e5
-	0x7ff75d0f8940
-	0x7ff75ced165d
-	0x7ff75cf29a33
-	0x7ff75cf29d3c
-	0x7ff75cf7df67
-	0x7ff75cf7ac97
-	0x7ff75cf1ac29
-	0x7ff75cf1ba93
-	0x7ff75d410640
-	0x7ff75d40af80
-	0x7ff75d4296e6
-	0x7ff75d115de4
-	0x7ff75d11ed8c
-	0x7ff75d102004
-	0x7ff75d1021b5
-	0x7ff75d0e7ee2
-	0x7ffe731ae8d7
-	0x7ffe7486c53c
-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:53:20</t>
+          <t>23/12/2025 10:04:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DK6</t>
+          <t>TK6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_demo_5</t>
+          <t>Giay th</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:53:32</t>
+          <t>23/12/2025 10:05:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DK7</t>
+          <t>TK7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_demo_6</t>
+          <t>Bánh bao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:53:41</t>
+          <t>23/12/2025 10:05:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DK8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>user_demo_7</t>
-        </is>
-      </c>
+          <t>TK8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03!</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Dép Nữ MWC 8620 - Dép Đế Bệt Nữ Mũi Tròn, Quai Da PU Bóng Mảnh Cách Điệu Đi Dạo Phố, Đi Làm Đơn Giản, Thanh Lịch.
+125.000 đ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:53:50</t>
+          <t>23/12/2025 10:05:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DK9</t>
+          <t>TK9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_demo_8</t>
+          <t>Giay!#$%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03 45216789</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:53:59</t>
+          <t>23/12/2025 10:05:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DK10</t>
+          <t>TK10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_demo_9</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03452167891</t>
+          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>Không tìm thấy sản phẩm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Abcde12345</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>số điện thoại không đúng định dạng!</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:54:10</t>
+          <t>23/12/2025 10:06:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DK11</t>
+          <t>TK11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_demo_10</t>
+          <t>Màu đen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Màu đen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>BALO MWC 1267 - Balo Unisex Phối Màu Đen, Be Thanh Lịch, Vừa Thời Trang Vừa Tiện Dụng Đựng Mọi Thứ Bạn Cần.
+180.000 đ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:55:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DK12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>user_demo_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1234567890abcdefghiklmno</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:55:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DK13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>user_demo_12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0912345679</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>mật khẩu không giống nhau</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:55:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DK14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0352146789</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tài khoản đã tồn tại trong hệ thống</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:55:34</t>
+          <t>23/12/2025 10:06:42</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,25 +1173,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1524,355 +1225,696 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TK1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
-195.000 đ</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21/12/2025 23:57:20</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:29:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TK2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>E196</t>
-        </is>
-      </c>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.
-195.000 đ</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21/12/2025 23:57:30</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:29:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TK3</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giày</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Giày</t>
-        </is>
-      </c>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
-275.000 đ</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21/12/2025 23:57:43</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:30:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TK4</t>
+          <t>DG4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GIÀY</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Giày</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC G299 - Giày Cao Gót Slingback Hở Gót, Bít Mũi Phủ Ánh Kim Bạc Lấp Lánh, Chuẩn Quý Cô Sang Trọng.
-275.000 đ</t>
-        </is>
-      </c>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21/12/2025 23:57:56</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:30:36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TK5</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giay the thao nam</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Giày thể thao nam</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Giày Thể Thao Nam MWC 5827 - Giày Thể Thao Sneaker Nam Cổ Thấp Đi Phượt, Leo Núi, Chạy Bộ Siêu Bền Đẹp, Đa Phong Cách.
-380.000 đ</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21/12/2025 23:58:06</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:31:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TK6</t>
+          <t>DG6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giay th</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:58:14</t>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập!</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:31:23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TK7</t>
+          <t>DG7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bánh bao</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21/12/2025 23:58:25</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:31:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TK8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>DG8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>abdc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dép Nữ MWC 8620 - Dép Đế Bệt Nữ Mũi Tròn, Quai Da PU Bóng Mảnh Cách Điệu Đi Dạo Phố, Đi Làm Đơn Giản, Thanh Lịch.
-125.000 đ</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi khi chạy testcase: Không thể mở sản phẩm đầu tiên [open_first_product]: Message: 
+</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:58:36</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:32:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TK9</t>
+          <t>DG9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Giay!#$%</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>!@#$%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/12/2025 23:58:46</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:32:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TK10</t>
+          <t>DG10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Giày Sandal Nữ MWC E196 - Sandal Nữ Hai Quai Ngang Kết Hợp Quai Dán Tiện Lợi, Cá Tính, Thoải Mái, Bền Đẹp.</t>
+          <t>032145678999</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Không tìm thấy sản phẩm</t>
+          <t>anhduong@gmail.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>21/12/2025 23:58:54</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:32:59</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TK11</t>
+          <t>DG11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Màu đen</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Màu đen</t>
+          <t>0321456789</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BALO MWC 1267 - Balo Unisex Phối Màu Đen, Be Thanh Lịch, Vừa Thời Trang Vừa Tiện Dụng Đựng Mọi Thứ Bạn Cần.
-180.000 đ</t>
+          <t>anh1@</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Giày xinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/12/2025 23:59:05</t>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DG12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>anh1@@</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:33:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DG13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0321456789</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>anh1@gmail.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Giày xinh</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Email không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Gửi bình luận thành công!</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:34:21</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,65 +1940,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -1965,398 +2017,1064 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DH1</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Thị Ánh Dương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>35</v>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>123 Lý Thường Kiệt</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>Phường Lái Hiếu</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>lâm đồng</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>22/12/2025 00:01:18</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:50:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DH2</t>
+          <t>TT2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>36</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>anhduong1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03321156788</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Quận 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Phường Bến Nghé</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>đà nẵng</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22/12/2025 00:01:57</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:50:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DH3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
+          <t>TT3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>39</v>
+          <t>duongduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>03321156790</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>TP Cần Thơ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Quận Ninh Kiều</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường An Bình</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>huế</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>22/12/2025 00:02:44</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:51:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DH4</t>
+          <t>TT4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>36</v>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2003</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Quận 2</t>
+          <t>Đồng Nai</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Phường An Khánh</t>
+          <t>Quận Ô Môn</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+          <t>Phường Long Hưng</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Đặt hàng thành công!</t>
+          <t>gia lai</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22/12/2025 00:03:12</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:51:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DH5</t>
+          <t>TT5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Phạm Dương</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>đen</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>39</v>
+          <t>anhanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>03321156770</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>905123456</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>123 ABC</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Chọn Tỉnh/Thành</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2005</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Hậu Giang</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
+          <t>Thị xã Ngã Bảy</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Bạn chưa nhập thông tin nhận hàng!</t>
-        </is>
-      </c>
+          <t>Phường Lái Hiếu</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Cập nhập tài khoản thành công!</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22/12/2025 00:03:45</t>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:51:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DH6</t>
+          <t>TT6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Cao Gót MWC 4444</t>
+          <t>Ánh Dương Phạm Thị</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bạc</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>37</v>
+          <t>anh12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nguyễn A</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3321156</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>456 DEF</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Chọn Quận/huyện</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chọn Xã/Phường</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:52:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TT7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>anh1@</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>03321156754</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Thành phố Tây Ninh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Phường 1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hà nội</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TT8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anh1@@</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>03321156790</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1997</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Huyện Trà Ôn</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Thị trấn Trà Ôn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vĩnh tuy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:53:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TT9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>anh1@gmail.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03321156789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>sóc sơn</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:54:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bình Phước</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Huyện Lộc Ninh</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Xã Lộc An</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>móng cái</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Vui lòng điền vào trường này.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:55:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TT11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Phạm Dương</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>anhduong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>lạng sơn</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:55:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TT12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>phamanh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tiền Giang</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Thành phố Mỹ Tho</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Phường 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quỳnh phụ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:55:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TT13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Phạm Ánh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>phamanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0332115678987</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Huyện Châu Thành</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Xã Đông Phước A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>thái bình</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TT14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>anh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>!#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>TP Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Quận 10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Phường Cầu Ông Lãnh</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SĐT không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Đặt hàng thành công!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Quận 2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phường Bến Nghé</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nghĩa lộ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Số điện thoại không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>×
+Thông báo
+Cập nhập tài khoản thành công!</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:04:12</t>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>23/12/2025 10:56:34</t>
         </is>
       </c>
     </row>
@@ -2371,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2382,75 +3100,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>District</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -2459,1064 +3167,398 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>DH1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phạm Thị Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>37</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2000</v>
+        <v>905123456</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>123 Lý Thường Kiệt</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Thị xã Ngã Bảy</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phường Lái Hiếu</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>lâm đồng</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:04:49</t>
+          <t>23/12/2025 11:21:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>DH2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phạm Ánh Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anhduong1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>03321156788</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2000</v>
+        <v>905123456</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TP Hồ Chí Minh</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Quận 1</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phường Bến Nghé</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>đà nẵng</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:05:09</t>
+          <t>23/12/2025 11:21:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TT3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>DH3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>duongduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>03321156790</t>
-        </is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2001</v>
+          <t>Phạm Ánh Dương</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TP Cần Thơ</t>
+          <t>Quận 1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Quận Ninh Kiều</t>
+          <t>Phường Bến Nghé</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phường An Bình</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>huế</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:05:28</t>
+          <t>23/12/2025 11:22:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>DH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>Giày Cao Gót MWC 4444</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2003</v>
+        <v>905123456</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Đồng Nai</t>
+          <t>Quận 2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Quận Ô Môn</t>
+          <t>Phường An Khánh</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phường Long Hưng</t>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>gia lai</t>
+          <t>Đặt hàng thành công!</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:06:03</t>
+          <t>23/12/2025 11:22:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TT5</t>
+          <t>DH5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phạm Dương</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anhanh@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>03321156770</t>
-        </is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Phạm Ánh Dương</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2005</v>
+        <v>905123456</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>123 ABC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chọn Tỉnh/Thành</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hậu Giang</t>
+          <t>Chọn Quận/huyện</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Thị xã Ngã Bảy</t>
+          <t>Chọn Xã/Phường</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phường Lái Hiếu</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:06:24</t>
+          <t>23/12/2025 11:23:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT6</t>
+          <t>DH6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm Thị</t>
+          <t>Giày Cao Gót MWC 4444</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anh12@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
+          <t>bạc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nguyễn A</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1999</v>
+        <v>3321156</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>456 DEF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TP Hồ Chí Minh</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chọn Tỉnh/Thành</t>
+          <t>Quận 10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chọn Quận/huyện</t>
+          <t>Phường 15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Chọn Xã/Phường</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>SĐT không đúng định dạng</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Bạn chưa nhập thông tin nhận hàng!</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cập nhập tài khoản thành công!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:07:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TT7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>anh1@</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>03321156754</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1995</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tây Ninh</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Thành phố Tây Ninh</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Phường 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hà nội</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>vui lòng nhập phần đứng sau '@'. 'anh1@' không hoàn chỉnh.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:07:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TT8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>anh1@@</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>03321156790</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1997</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Vĩnh Long</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Huyện Trà Ôn</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Thị trấn Trà Ôn</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>vĩnh tuy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>phần đứng sau '@' không được chứa biểu tượng '@'.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:08:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TT9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>anh1@gmail.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>03321156789</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2003</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>sóc sơn</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>'.' bị sử dụng sai vị trí trong 'gmail.'.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:09:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2004</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bình Phước</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Huyện Lộc Ninh</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Xã Lộc An</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>móng cái</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:09:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TT11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Phạm Dương</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>anhduong@gmail.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>abcd</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2005</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>lạng sơn</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:10:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TT12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Phạm Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>phamanh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Tiền Giang</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Thành phố Mỹ Tho</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Phường 10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>quỳnh phụ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:10:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TT13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Phạm Ánh</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>phamanh@gmail.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0332115678987</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2007</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Hậu Giang</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Huyện Châu Thành</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Xã Đông Phước A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>thái bình</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:10:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TT14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Phạm Thị Ánh Dương</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>anh1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>!#$%^&amp;*()</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>TP Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Quận 2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Phường Bến Nghé</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>nghĩa lộ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Số điện thoại không hợp lệ.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>×
-Thông báo
-Cập nhập tài khoản thành công!</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:10:59</t>
+          <t>23/12/2025 11:23:46</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3542,7 +3584,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3552,40 +3594,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>PasswordConfirm</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
@@ -3594,721 +3626,642 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>DK1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Pham_Thanh_An</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>0359694533</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Pham_Thanh_An</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Pham_Thanh_An</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:16:41</t>
+          <t>23/12/2025 14:43:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DG2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
+          <t>DK2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>user_demo_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:17:04</t>
+          <t>23/12/2025 14:44:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DG3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>DK3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:17:31</t>
+          <t>23/12/2025 14:44:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DG4</t>
+          <t>DK4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:17:55</t>
+          <t>23/12/2025 14:44:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DG5</t>
+          <t>DK5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Vui lòng điền vào trường này.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">Tên người dùng khác mong đợi: </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:18:21</t>
+          <t>23/12/2025 14:44:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DG6</t>
+          <t>DK6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>091</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>Abcde12345</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Số điện thoại không đúng định dạng!</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Vui lòng nhập!</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:18:49</t>
+          <t>23/12/2025 14:44:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DG7</t>
+          <t>DK7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:19:17</t>
+          <t>23/12/2025 14:45:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DG8</t>
+          <t>DK8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abdc</t>
+          <t>03!</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:19:45</t>
+          <t>23/12/2025 14:45:24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DG9</t>
+          <t>DK9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>!@#$%</t>
+          <t>03 45216789</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:20:17</t>
+          <t>23/12/2025 14:45:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DG10</t>
+          <t>DK10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>032145678999</t>
+          <t>03452167891</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anhduong@gmail.com</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>Abcde12345</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>số điện thoại không đúng định dạng!</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Số điện thoại không hợp lệ</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:20:50</t>
+          <t>23/12/2025 14:45:47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DG11</t>
+          <t>DK11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>anh1@_x000d_</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Email không đúng định dạng</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:21:23</t>
+          <t>23/12/2025 14:46:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DG12</t>
+          <t>DK12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>user_demo_11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0321456789</t>
+          <t>0912345679</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anh1@@_x000d_</t>
+          <t>1234567890abcdefghiklmno</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Giày xinh</t>
+          <t>1234567890abcdefghiklmno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
+          <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Email không đúng định dạng</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:21:58</t>
+          <t>23/12/2025 14:46:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DG13</t>
+          <t>DK13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>user_demo_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0912345679</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mật khẩu không giống nhau</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23/12/2025 14:46:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DK14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Ánh Dương Phạm</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0321456789</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>anh1@gmail._x000d_</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Giày xinh</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Giày rất đẹp, vừa form chân, y như hình</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Email không đúng định dạng</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Gửi bình luận thành công!</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>22/12/2025 00:22:25</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>035214679</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tài khoản đã tồn tại trong hệ thống</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>23/12/2025 14:46:47</t>
         </is>
       </c>
     </row>
